--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount.xlsx
@@ -29,27 +29,6 @@
     <t>子产品代码*</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>此产品优惠调整（补充性）描述文字</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（一产多费时必填、一费多产时不必填）</t>
-    </r>
-  </si>
-  <si>
     <t>优惠的费用*</t>
   </si>
   <si>
@@ -63,27 +42,6 @@
   </si>
   <si>
     <t>优惠截止时间</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>对此费率优惠调整（补充性）描述文字</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（一费多产时必填、一产多费时不必填）</t>
-    </r>
   </si>
   <si>
     <t>报告发布日期（YYYY/MM/DD)*</t>
@@ -99,6 +57,14 @@
   </si>
   <si>
     <t>更新人</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>对此费率优惠调整描述文字</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>此产品优惠调整描述文字</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -568,9 +534,9 @@
     <col min="10" max="10" width="33" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -579,34 +545,34 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="J1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="13" t="s">
+      <c r="L1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="9" t="s">
-        <v>11</v>
-      </c>
       <c r="M1" s="9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" x14ac:dyDescent="0.25">

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18530" windowHeight="7130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18525" windowHeight="7125"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -60,12 +60,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>对此费率优惠调整描述文字</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>此产品优惠调整描述文字</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>单产品多费率描述文字</t>
+  </si>
+  <si>
+    <t>单费率多产品描述文字</t>
   </si>
 </sst>
 </file>
@@ -522,19 +520,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.36328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="36.90625" style="1" customWidth="1"/>
-    <col min="4" max="6" width="10.90625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="27.26953125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25.08984375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="33.7265625" customWidth="1"/>
+    <col min="2" max="2" width="11.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="36.875" style="1" customWidth="1"/>
+    <col min="4" max="6" width="10.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="33.75" customWidth="1"/>
     <col min="10" max="10" width="33" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -545,7 +543,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>2</v>
@@ -563,7 +561,7 @@
         <v>6</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K1" s="13" t="s">
         <v>7</v>
@@ -575,7 +573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -599,7 +597,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -610,7 +608,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdFeediscount.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>产品登记编码*</t>
   </si>
@@ -64,6 +64,10 @@
   </si>
   <si>
     <t>单费率多产品描述文字</t>
+  </si>
+  <si>
+    <t>子产品名称</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -519,20 +523,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="36.875" style="1" customWidth="1"/>
-    <col min="4" max="6" width="10.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="27.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="33.75" customWidth="1"/>
-    <col min="10" max="10" width="33" style="12" customWidth="1"/>
+    <col min="3" max="4" width="36.875" style="1" customWidth="1"/>
+    <col min="5" max="7" width="10.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="27.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="33.75" customWidth="1"/>
+    <col min="11" max="11" width="33" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:14" ht="25.5" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -542,50 +546,54 @@
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="L1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:14" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="7"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="9"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="11"/>
       <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
